--- a/docs/sprint3/test-cases.xlsx
+++ b/docs/sprint3/test-cases.xlsx
@@ -69,7 +69,7 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00375623"/>
+      <color rgb="00B25900"/>
       <sz val="10"/>
     </font>
     <font>
@@ -83,7 +83,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -106,6 +106,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
         <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -183,25 +189,25 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -583,8 +589,8 @@
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
   </cols>
@@ -592,14 +598,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ДОСЬЄ ЯКОСТІ v3 — НАБІР ТЕСТ-КЕЙСІВ (Спринт 3)</t>
+          <t>ДОСЬЄ ЯКОСТІ v3 — НАБІР ТЕСТ-КЕЙСІВ (Спринт 3 — Чернетка)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Команда: BMIBM-banking | Продукт: «ФінКит» (finkit) | Demo: ParaBank | Автор: Тест-аналітик | Норматив: ≥ 20 кейсів</t>
+          <t>Команда: BMIBM-banking | Продукт: «ФінКит» (finkit) | Demo: ParaBank | Автор: Мажуга Ілля (ТА) | Призначений рецензент: Городиська Анна (СМ)</t>
         </is>
       </c>
     </row>
@@ -715,22 +721,18 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr"/>
       <c r="L5" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -783,22 +785,18 @@
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr"/>
       <c r="L6" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -850,22 +848,18 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr"/>
       <c r="L7" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -917,22 +911,18 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K8" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr"/>
       <c r="L8" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -984,22 +974,18 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr"/>
       <c r="L9" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1052,22 +1038,18 @@
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr"/>
       <c r="L10" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1117,22 +1099,18 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr"/>
       <c r="L11" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1184,22 +1162,18 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr"/>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1253,22 +1227,18 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
       <c r="L13" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1321,22 +1291,18 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K14" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K14" s="11" t="inlineStr"/>
       <c r="L14" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1355,18 @@
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K15" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
       <c r="L15" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1457,22 +1419,18 @@
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K16" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr"/>
       <c r="L16" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1525,22 +1483,18 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
       <c r="L17" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1593,22 +1547,18 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J18" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K18" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr"/>
       <c r="L18" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1660,22 +1610,18 @@
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr"/>
       <c r="L19" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1728,22 +1674,18 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J20" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K20" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr"/>
       <c r="L20" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1796,22 +1738,18 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr"/>
       <c r="L21" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1863,22 +1801,18 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1931,22 +1865,18 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr"/>
       <c r="L23" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -1998,22 +1928,18 @@
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -2064,22 +1990,18 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr"/>
       <c r="L25" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -2132,22 +2054,18 @@
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>Тест-аналітик</t>
+          <t>Мажуга Ілля</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr">
-        <is>
-          <t>12.10.2026</t>
-        </is>
-      </c>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2105,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Трасування функціональних, GUI, BL та нефункціональних вимог продукту «ФінКит» до тест-кейсів Спринта 3</t>
+          <t>Трасування функціональних, GUI, BL та нефункціональних вимог продукту «ФінКит» до тест-кейсів Спринта 3 (Чернетки)</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2164,7 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -2278,7 +2196,7 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -2310,7 +2228,7 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2342,7 +2260,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -2374,7 +2292,7 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
@@ -2406,7 +2324,7 @@
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -2438,7 +2356,7 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
@@ -2470,7 +2388,7 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -2502,7 +2420,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -2534,7 +2452,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -2566,7 +2484,7 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -2598,7 +2516,7 @@
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -2630,7 +2548,7 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
@@ -2662,7 +2580,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -2694,7 +2612,7 @@
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -2726,7 +2644,7 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -2758,7 +2676,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -2790,7 +2708,7 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -2822,7 +2740,7 @@
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -2854,7 +2772,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -2886,7 +2804,7 @@
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -3110,7 +3028,7 @@
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Покрито</t>
+          <t>Покрито (draft)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -3170,24 +3088,24 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ЖУРНАЛ РЕЦЕНЗУВАННЯ ТЕСТ-КЕЙСІВ («Review»)</t>
+          <t>ЖУРНАЛ РЕЦЕНЗУВАННЯ ТЕСТ-КЕЙСІВ («Review» — На рецензію)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Результати перевірки кожного тест-кейсу Скрам-майстром / Рецензентом за Чек-листом 13.1 (8 пунктів)</t>
+          <t>Заготовлені рядки для рецензування кейсів Городиською Анною (Скрам-майстер / Рецензент) за Чек-листом 13.1</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3117,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Рецензент</t>
+          <t>Призначений рецензент</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -3214,7 +3132,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Виправлено автором</t>
+          <t>Виправлено автором (Мажуга І.)</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -3231,27 +3149,27 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Усі 8 пунктів чек-листа виконано. Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3263,27 +3181,27 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Додати конкретне значення логіна в кроки.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3295,27 +3213,27 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Уточнювати текст помилки згідно з GUI-30.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3327,27 +3245,27 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Зауважень немає. Кейс незалежний.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3359,27 +3277,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Зауважень немає. Очікуваний результат відповідає SRS.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3391,27 +3309,27 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3423,27 +3341,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3455,27 +3373,27 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Уточнити назву фільтра у кроках.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3487,27 +3405,27 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3519,27 +3437,27 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Додати перевірку зміни балансу в очікуваний результат.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F14" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3551,27 +3469,27 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Вказати граничне значення суми у заголовку.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F15" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3583,27 +3501,27 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Обґрунтувати вибір значення 0 грн.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3615,27 +3533,27 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Перевірено згідно з вимогами BL-40 / F-70.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3647,27 +3565,27 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3679,27 +3597,27 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3711,27 +3629,27 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3743,27 +3661,27 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3775,27 +3693,27 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3807,27 +3725,27 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Уточнити початковий внесок 500 грн у кроці 2.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3839,27 +3757,27 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Граничне значення min-1 (499 грн) вказано вірно.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F24" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3871,27 +3789,27 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>
@@ -3903,27 +3821,27 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Скрам-майстер</t>
+          <t>Городиська Анна</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>12.10.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Зауважень немає.</t>
+          <t>Очікує перевірки</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Ні</t>
         </is>
       </c>
       <c r="F26" s="9" t="inlineStr">
         <is>
-          <t>reviewed</t>
+          <t>draft</t>
         </is>
       </c>
     </row>

--- a/docs/sprint3/test-cases.xlsx
+++ b/docs/sprint3/test-cases.xlsx
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -607,14 +607,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ДОСЬЄ ЯКОСТІ v3 — НАБІР ТЕСТ-КЕЙСІВ (Спринт 3 — Оновлено автором)</t>
+          <t>ДОСЬЄ ЯКОСТІ v3 — НАБІР ТЕСТ-КЕЙСІВ (Спринт 3 — Оновлено з граничними значеннями)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Команда: BMIBM-banking | Продукт: «ФінКит» (finkit) | Demo: ParaBank | Автор: Мажуга Ілля (ТА) | Рецензент: Городиська Анна (СМ)</t>
+          <t>Команда: BMIBM-banking | Продукт: «ФінКит» (finkit) | Demo: ParaBank | Автор: Мажуга Ілля (ТА) | Рецензент: Городиська Анна (СМ) | Всього кейсів: 26</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1284,23 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>F-70, BL-40</t>
+          <t>F-70</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Успішний переказ коштів 100 000 грн між власними рахунками (граничне значення)</t>
+          <t>Успішний переказ коштів 500 грн між власними рахунками</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Авторизований BMIBM_user1 має два рахунки (Рахунок A з балансом ≥ 100 000 грн, Рахунок B). Браузер Chrome.</t>
+          <t>Авторизований BMIBM_user1 має два рахунки (Рахунок A з балансом ≥ 500 грн, Рахунок B). Браузер Chrome.</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
           <t>1. Відкрити https://parabank.parasoft.com/parabank/transfer.htm
-2. У поле Amount ввести «100000» (граничне значення: рівно денний ліміт 100 000 грн).
+2. У поле Amount ввести «500».
 3. Обрати From account (Рахунок A) та To account (Рахунок B).
 4. Натиснути кнопку «Transfer».
 5. Вийти з системи.</t>
@@ -1308,9 +1308,9 @@
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>1. Сторінка переказу відкрита.
+          <t>1. Сторінку переказу відкрито.
 2-3. Поля заповнено.
-4. З'являється повідомлення «Transfer Complete!», показано суму 100 000 грн та номери рахунків; баланс A зменшився на 100 000 грн, B — збільшився на 100 000 грн.
+4. З'являється повідомлення «Transfer Complete!», показано суму 500 грн та номери рахунків; баланс A зменшився на 500 грн, B — збільшився на 500 грн.
 5. Вихід виконано.</t>
         </is>
       </c>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>Негативна перевірка переказу з нульовою сумою (0 грн - граничне значення)</t>
+          <t>Негативна перевірка переказу з нульовою сумою (0 грн - нижня недійсна межа)</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Негативна перевірка переказу при перевищенні денного ліміту (100 001 грн)</t>
+          <t>Негативна перевірка переказу при перевищенні денного ліміту (100 001 грн - верхня недійсна межа)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1495,7 +1495,7 @@
       <c r="E17" s="6" t="inlineStr">
         <is>
           <t>1. Відкрити https://parabank.parasoft.com/parabank/transfer.htm
-2. У поле Amount ввести «100001» (недійсне граничне величина: ліміт 100 000 + 1 грн).
+2. У поле Amount ввести «100001» (гранична величина: верхній ліміт 100 000 + 1 грн).
 3. Обрати рахунки.
 4. Натиснути «Transfer».
 5. Закрити вкладку.</t>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Подання заявки на кредит на мінімальну суму 500 грн (нижня межа дозволеного)</t>
+          <t>Подання заявки на кредит на суму 500 грн (нижня дійсна межа дозволеного)</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1882,7 +1882,7 @@
       <c r="E23" s="6" t="inlineStr">
         <is>
           <t>1. Відкрити https://parabank.parasoft.com/parabank/requestloan.htm
-2. У поле Loan Amount ввести «500» (гранична величина: мінімальна дозволена сума 500 грн), Down Payment «50».
+2. У поле Loan Amount ввести «500» (граничне значення: min 500 грн), Down Payment «50».
 3. Обрати рахунок-джерело внеску.
 4. Натиснути «Apply Now».
 5. Вийти з системи.</t>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Негативна перевірка заявки на кредит з сумою 499 грн (граничне значення: min - 1)</t>
+          <t>Негативна перевірка заявки на кредит з сумою 499 грн (нижня недійсна межа: min - 1)</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -1947,7 +1947,7 @@
       <c r="E24" s="12" t="inlineStr">
         <is>
           <t>1. Відкрити https://parabank.parasoft.com/parabank/requestloan.htm
-2. У поле Loan Amount ввести «499» (недійсне граничне значення: min 500 - 1 грн), Down Payment «50».
+2. У поле Loan Amount ввести «499» (граничне значення: min 500 - 1 грн), Down Payment «50».
 3. Обрати рахунок та натиснути «Apply Now».
 4. Закрити вкладку.</t>
         </is>
@@ -2109,6 +2109,330 @@
       </c>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="65" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>F-70, BL-40</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Успішний переказ коштів 99 999 грн між власними рахунками (верхня дійсна межа: limit - 1)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Авторизований BMIBM_user1 має два рахунки (Рахунок A з балансом ≥ 100 000 грн, Рахунок B). Браузер Chrome.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>1. Відкрити https://parabank.parasoft.com/parabank/transfer.htm
+2. У поле Amount ввести «99999» (граничне значення: денний ліміт 100 000 - 1 грн).
+3. Обрати From account (Рахунок A) та To account (Рахунок B).
+4. Натиснути кнопку «Transfer».
+5. Вийти з системи.</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>1. Сторінку переказу відкрито.
+2-3. Поля заповнено.
+4. З'являється повідомлення «Transfer Complete!», показано суму 99 999 грн та номери рахунків; баланс A зменшився на 99 999 грн, B — збільшився на 99 999 грн.
+5. Вихід виконано.</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Позитивний</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Мажуга Ілля</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr"/>
+      <c r="L27" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="65" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>F-70, BL-40</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Успішний переказ коштів 100 000 грн між власними рахунками (точна верхня дійсна межа: limit)</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Авторизований BMIBM_user1 має два рахунки (Рахунок A з балансом ≥ 100 000 грн, Рахунок B). Браузер Chrome.</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>1. Відкрити https://parabank.parasoft.com/parabank/transfer.htm
+2. У поле Amount ввести «100000» (граничне значення: точний денний ліміт 100 000 грн).
+3. Обрати From account (Рахунок A) та To account (Рахунок B).
+4. Натиснути кнопку «Transfer».
+5. Вийти з системи.</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>1. Сторінку переказу відкрито.
+2-3. Поля заповнено.
+4. З'являється повідомлення «Transfer Complete!», показано суму 100 000 грн та номери рахунків; баланс A зменшився на 100 000 грн, B — збільшився на 100 000 грн.
+5. Вихід виконано.</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>Позитивний</t>
+        </is>
+      </c>
+      <c r="I28" s="11" t="inlineStr">
+        <is>
+          <t>Мажуга Ілля</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr"/>
+      <c r="L28" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="65" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>F-110, BL-30</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Подання заявки на кредит на суму 501 грн (нижня дійсна межа: min + 1)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Авторизований BMIBM_user1 з наявним рахунком. Браузер Chrome.</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>1. Відкрити https://parabank.parasoft.com/parabank/requestloan.htm
+2. У поле Loan Amount ввести «501» (граничне значення: min 500 + 1 грн), Down Payment «50».
+3. Обрати рахунок-джерело внеску.
+4. Натиснути «Apply Now».
+5. Вийти з системи.</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>1. Сторінку заявки на кредит відкрито.
+2-3. Параметри заповнено.
+4. Заявку прийнято, відображено рішення скорингу («Approved» / «Denied») та номер нового кредитного рахунку при схваленні.
+5. Вихід виконано.</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>Позитивний</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Мажуга Ілля</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr"/>
+      <c r="L29" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="65" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>F-110, BL-30</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Подання заявки на кредит на суму 1 000 000 грн (верхня дійсна межа: max limit)</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Авторизований BMIBM_user1 з наявним рахунком. Браузер Chrome.</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>1. Відкрити https://parabank.parasoft.com/parabank/requestloan.htm
+2. У поле Loan Amount ввести «1000000» (граничне значення: максимальна дозволена сума кредиту 1 000 000 грн), Down Payment «100000».
+3. Обрати рахунок-джерело внеску.
+4. Натиснути «Apply Now».
+5. Вийти з системи.</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>1. Сторінку заявки на кредит відкрито.
+2-3. Параметри заповнено.
+4. Заявку прийнято до обробки, виведено рішення скорингу та створення рахунку.
+5. Вихід виконано.</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Позитивний</t>
+        </is>
+      </c>
+      <c r="I30" s="11" t="inlineStr">
+        <is>
+          <t>Мажуга Ілля</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr"/>
+      <c r="L30" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="65" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>F-110, BL-30</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Негативна перевірка заявки на кредит з сумою 1 000 001 грн (верхня недійсна межа: max + 1)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Авторизований BMIBM_user1. Максимальна сума за SRS F-110 становить 1 000 000 грн. Браузер Chrome.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>1. Відкрити https://parabank.parasoft.com/parabank/requestloan.htm
+2. У поле Loan Amount ввести «1000001» (граничне значення: max 1 000 000 + 1 грн), Down Payment «100000».
+3. Обрати рахунок та натиснути «Apply Now».
+4. Закрити вкладку.</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>1. Сторінку відкрито.
+2-3. Введено 1 000 001 грн.
+4. Заявка не приймається / відхиляється з повідомленням про перевищення максимального суми кредиту в 1 000 000 грн.
+5. Сесію закрито.</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>Негативний</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Мажуга Ілля</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr"/>
+      <c r="L31" s="15" t="inlineStr">
         <is>
           <t>draft</t>
         </is>
@@ -2135,7 +2459,7 @@
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
   </cols>
@@ -2396,7 +2720,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>TC-010, TC-011, TC-012, TC-013</t>
+          <t>TC-010, TC-011, TC-012, TC-013, TC-023, TC-024</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -2406,7 +2730,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>Позитивний переказ, граничні значення (0, &gt;баланс, &gt;ліміт)</t>
+          <t>Позитивний переказ, повне покриття меж (0, &gt;баланс, 99 999, 100 000, 100 001)</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2843,12 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Заявка на кредит (мін. 500 грн) та швидке рішення</t>
+          <t>Заявка на кредит (межі 500 грн – 1 000 000 грн) та швидке рішення</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>TC-019, TC-020</t>
+          <t>TC-019, TC-020, TC-025, TC-026, TC-027</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -2534,7 +2858,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>Схвалення 500 грн та негативна межа 499 грн</t>
+          <t>Повне покриття меж кредиту: 499, 500, 501, 1 000 000, 1 000 001 грн</t>
         </is>
       </c>
     </row>
@@ -2844,7 +3168,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>TC-019</t>
+          <t>TC-019, TC-025..TC-027</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -2908,17 +3232,17 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="inlineStr">
-        <is>
-          <t>Не покрито у С3</t>
+          <t>TC-019, TC-020, TC-025..027</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>Покрито частково</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>Бізнес-логіка Java-модуля покривається юніт-тестами у Спринті 4</t>
+          <t>Перевірено межі кредитування 499, 500, 501, 1M, 1M+1; решта у С4</t>
         </is>
       </c>
     </row>
@@ -2940,17 +3264,17 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="inlineStr">
-        <is>
-          <t>Не покрито у С3</t>
+          <t>TC-010..013, TC-023, TC-024</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>Покрито частково</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Бізнес-логіка Java-модуля покривається юніт-тестами у Спринті 4</t>
+          <t>Перевірено межі переказу 0, &gt;баланс, 99 999, 100 000, 100 001 грн; решта у С4</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3392,7 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>TC-001..TC-022</t>
+          <t>TC-001..TC-027</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
@@ -3129,7 +3453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3492,7 +3816,7 @@
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Порушено п. 3 (немає URL), п. 4 (бракує браузера) та п. 8 (додати граничні перевірки на суми 99 999 та 100 000).</t>
+          <t>Порушено п. 3 (немає URL) та п. 4 (бракує браузера). Залишено базовий кейс на 500 грн.</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
@@ -3556,7 +3880,7 @@
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Порушено п. 3 (немає URL у Кроці 1) та п. 4 (бракує браузера в передумовах).</t>
+          <t>Порушено п. 3 (немає URL у Кроці 1) та п. 4 (бракує браузера в передумовах). Нижня недійсна межа (0 грн).</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
@@ -3588,7 +3912,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>Порушено п. 3 (немає URL), п. 4 (бракує браузера) та п. 8 (додати граничні перевірки ліміту).</t>
+          <t>Порушено п. 3 (немає URL), п. 4 (бракує браузера). Перевірено верхню недійсну межу ліміту (100 001 грн).</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -3780,7 +4104,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>Порушено п. 3 (немає URL), п. 4 (бракує браузера) та п. 8 (додати кейси на суми кредиту: 500, 501, 1 000 000, 1 000 001).</t>
+          <t>Порушено п. 3 (немає URL), п. 4 (бракує браузера). Перевірено нижню дійсну межу кредиту (500 грн).</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -3812,7 +4136,7 @@
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Порушено п. 3 (немає URL у Кроці 1), п. 4 (бракує браузера в передумовах) та п. 8 (бракує граничних значень).</t>
+          <t>Порушено п. 3 (немає URL у Кроці 1), п. 4 (бракує браузера). Перевірено нижню недійсну межу кредиту (499 грн).</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -3885,6 +4209,166 @@
         </is>
       </c>
       <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TC-023</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>27.10.2026</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>Додано окремий кейс за зауваженням рецензента: верхня дійсна межа ліміту переказу (99 999 грн, limit - 1).</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>TC-024</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>27.10.2026</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Додано окремий кейс за зауваженням рецензента: точна верхня дійсна межа ліміту переказу (100 000 грн, limit).</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TC-025</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>27.10.2026</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Додано окремий кейс за зауваженням рецензента: нижня дійсна межа кредиту (501 грн, min + 1).</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>TC-026</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>27.10.2026</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Додано окремий кейс за зауваженням рецензента: верхня дійсна межа кредиту (1 000 000 грн, max limit).</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TC-027</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Городиська Анна</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>27.10.2026</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>Додано окремий кейс за зауваженням рецензента: верхня недійсна межа кредиту (1 000 001 грн, max + 1).</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Так</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
         <is>
           <t>draft</t>
         </is>

--- a/docs/sprint3/test-cases.xlsx
+++ b/docs/sprint3/test-cases.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Test cases" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="669" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="304">
   <si>
     <t xml:space="preserve">ДОСЬЄ ЯКОСТІ v3 — НАБІР ТЕСТ-КЕЙСІВ (Спринт 3 — Оновлено з граничними значеннями)</t>
   </si>
@@ -136,9 +136,6 @@
     <t xml:space="preserve">Негативний</t>
   </si>
   <si>
-    <t xml:space="preserve">draft</t>
-  </si>
-  <si>
     <t xml:space="preserve">TC-003</t>
   </si>
   <si>
@@ -1108,8 +1105,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy"/>
   </numFmts>
   <fonts count="15">
     <font>
@@ -1206,12 +1204,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
       <sz val="10"/>
-      <color rgb="FFB25900"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1221,7 +1217,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1255,13 +1251,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -1329,76 +1319,92 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1431,8 +1437,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF4F7FA"/>
+      <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -1465,7 +1471,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FFB25900"/>
+      <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF375623"/>
@@ -1657,1071 +1663,1113 @@
   <dimension ref="A1:L31"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="K4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L5" s="9" t="s">
+      <c r="J5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="15" t="s">
+      <c r="J6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="B8" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="5"/>
-      <c r="L7" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="13" t="s">
+      <c r="J9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G10" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H11" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="11" t="s">
+      <c r="I11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="7" t="s">
+      <c r="J11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H13" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="J15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G20" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="G10" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="H20" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I20" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="7" t="s">
+      <c r="J20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K21" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H23" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I23" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="J23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K23" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I12" s="11" t="s">
+      <c r="I25" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="J25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="8" t="s">
+      <c r="H27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="13" t="s">
+      <c r="J27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="11" t="s">
+      <c r="I28" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="J28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I31" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="5"/>
-      <c r="L15" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" s="5"/>
-      <c r="L17" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J18" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J20" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K21" s="5"/>
-      <c r="L21" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J22" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K23" s="5"/>
-      <c r="L23" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J24" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K25" s="5"/>
-      <c r="L25" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I26" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J26" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="5"/>
-      <c r="L27" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J28" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K29" s="5"/>
-      <c r="L29" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="J30" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="15" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>166</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>32</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K31" s="5"/>
-      <c r="L31" s="15" t="s">
-        <v>33</v>
+      <c r="J31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -2747,632 +2795,632 @@
   <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="F4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="F5" s="6" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="13" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C6" s="12" t="s">
+      <c r="D6" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="E6" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F6" s="12" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F7" s="6" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="B8" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="D8" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F8" s="12" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="D9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F9" s="6" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="B10" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>193</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="12" t="s">
+      <c r="D10" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F10" s="12" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="D11" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="E11" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F11" s="6" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="B12" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="B12" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="D12" s="12" t="s">
         <v>200</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F12" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F12" s="12" t="s">
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="D13" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F13" s="6" t="s">
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="D14" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F14" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F14" s="12" t="s">
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
+      <c r="B15" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C15" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F15" s="6" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F16" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F16" s="12" t="s">
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="B17" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="D17" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F17" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F17" s="6" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+      <c r="B18" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="C18" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="B18" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F18" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F18" s="12" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="D19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F19" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F19" s="6" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+      <c r="B20" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C20" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="D20" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F20" s="13" t="s">
         <v>225</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F20" s="12" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="7" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="E21" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F21" s="6" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+      <c r="B22" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C22" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C22" s="12" t="s">
+      <c r="D22" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F22" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F22" s="12" t="s">
+    </row>
+    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+      <c r="B23" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="D23" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="F23" s="6" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
+      <c r="B24" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="B24" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C24" s="12" t="s">
+      <c r="D24" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F24" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F24" s="12" t="s">
+    </row>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
+      <c r="B25" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="D25" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F25" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="E25" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="6" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
+      <c r="B26" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="C26" s="12" t="s">
+      <c r="D26" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="E26" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="F26" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="F26" s="12" t="s">
+    </row>
+    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="D27" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="E27" s="8" t="s">
+      <c r="F27" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="F27" s="6" t="s">
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
+      <c r="B28" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>254</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C28" s="12" t="s">
+      <c r="D28" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="E28" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="F28" s="13" t="s">
         <v>256</v>
       </c>
-      <c r="E28" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="F28" s="12" t="s">
+    </row>
+    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
+      <c r="B29" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="D29" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F29" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="F29" s="6" t="s">
+    </row>
+    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
+      <c r="B30" s="12" t="s">
         <v>262</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="C30" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="C30" s="12" t="s">
+      <c r="D30" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F30" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="E30" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="F30" s="12" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
+      <c r="B31" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>266</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="C31" s="6" t="s">
+      <c r="D31" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="F31" s="6" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="11" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+      <c r="B32" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C32" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="C32" s="12" t="s">
+      <c r="D32" s="12" t="s">
         <v>270</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="E32" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="13" t="s">
         <v>271</v>
       </c>
-      <c r="E32" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="F32" s="12" t="s">
+    </row>
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="C33" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="D33" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>275</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="E33" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3398,591 +3446,591 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="F4" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="F5" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="F5" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="12" t="s">
+      <c r="E6" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="F6" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>285</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="13" t="s">
         <v>289</v>
       </c>
-      <c r="E7" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="12" t="s">
+      <c r="E12" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="F13" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="13" t="s">
         <v>290</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="12" t="s">
+      <c r="E14" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="E14" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="12" t="s">
+      <c r="E16" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>293</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="E17" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="E19" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>291</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>292</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D24" s="13" t="s">
         <v>296</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
-        <v>129</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="E24" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="12" t="s">
+      <c r="E26" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="E26" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="E27" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>300</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="D28" s="12" t="s">
+      <c r="E28" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D29" s="7" t="s">
         <v>301</v>
       </c>
-      <c r="E28" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="E29" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>302</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="D30" s="12" t="s">
+      <c r="E30" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="E30" s="11" t="s">
-        <v>288</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="F31" s="9" t="s">
+      <c r="E31" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>25</v>
       </c>
     </row>
